--- a/cypress/fixtures/File/generated-ai/Canteen Agreement.xlsx
+++ b/cypress/fixtures/File/generated-ai/Canteen Agreement.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="96">
   <si>
     <t>name</t>
   </si>
@@ -130,6 +130,9 @@
     <t>PO No.</t>
   </si>
   <si>
+    <t>Capex No.</t>
+  </si>
+  <si>
     <t>Business Risks (If Any)</t>
   </si>
   <si>
@@ -160,9 +163,15 @@
     <t>Fixed Term</t>
   </si>
   <si>
+    <t>Initial Renewal Date</t>
+  </si>
+  <si>
     <t>Contract Expiration Date</t>
   </si>
   <si>
+    <t>Date of Main Agreement</t>
+  </si>
+  <si>
     <t>Term (In Month Or Years)</t>
   </si>
   <si>
@@ -193,6 +202,30 @@
     <t>if Registered office option is selected in above field</t>
   </si>
   <si>
+    <t>Counterparty Corporate Office Address</t>
+  </si>
+  <si>
+    <t>if Corporate office option is selected in above field</t>
+  </si>
+  <si>
+    <t>Head Office Address</t>
+  </si>
+  <si>
+    <t>if Head office option is selected in above field</t>
+  </si>
+  <si>
+    <t>Branch Office Address</t>
+  </si>
+  <si>
+    <t>if Branch office option is selected in above field</t>
+  </si>
+  <si>
+    <t>Principal Office Address</t>
+  </si>
+  <si>
+    <t>if Principal office option is selected in above field</t>
+  </si>
+  <si>
     <t>Counterparty GSTIN No.</t>
   </si>
   <si>
@@ -242,6 +275,18 @@
   </si>
   <si>
     <t>file</t>
+  </si>
+  <si>
+    <t>Capex</t>
+  </si>
+  <si>
+    <t>CDA</t>
+  </si>
+  <si>
+    <t>NDA</t>
+  </si>
+  <si>
+    <t>PAN No.</t>
   </si>
   <si>
     <t>MSME No.</t>
@@ -634,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -858,18 +903,18 @@
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
         <v>41</v>
-      </c>
-      <c r="B21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -877,43 +922,43 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
         <v>44</v>
       </c>
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
         <v>47</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
         <v>49</v>
       </c>
-      <c r="B25" t="s">
-        <v>45</v>
-      </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -921,10 +966,10 @@
         <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -932,10 +977,10 @@
         <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -943,15 +988,15 @@
         <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -962,7 +1007,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -973,10 +1018,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" t="s">
         <v>56</v>
-      </c>
-      <c r="B31" t="s">
-        <v>57</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
@@ -984,10 +1029,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
         <v>15</v>
@@ -995,7 +1040,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -1006,32 +1051,32 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" t="s">
         <v>62</v>
       </c>
-      <c r="B35" t="s">
-        <v>63</v>
-      </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" t="s">
         <v>64</v>
-      </c>
-      <c r="B36" t="s">
-        <v>14</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
@@ -1042,18 +1087,18 @@
         <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
         <v>15</v>
@@ -1061,18 +1106,18 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -1083,7 +1128,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -1094,18 +1139,18 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -1116,57 +1161,178 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>80</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>88</v>
+      </c>
+      <c r="B53" t="s">
+        <v>86</v>
+      </c>
+      <c r="C53" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>90</v>
+      </c>
+      <c r="B55" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>91</v>
+      </c>
+      <c r="B56" t="s">
+        <v>86</v>
+      </c>
+      <c r="C56" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>92</v>
+      </c>
+      <c r="B57" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>93</v>
+      </c>
+      <c r="B58" t="s">
+        <v>86</v>
+      </c>
+      <c r="C58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>94</v>
+      </c>
+      <c r="B59" t="s">
+        <v>86</v>
+      </c>
+      <c r="C59" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
